--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0042.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0042.xlsx
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Ta biết. Chỉ nghĩ đến viễn cảnh đó thôi đã khiến ta rùng mình, chân run rẩy khi đối mặt với lũ quái vật ấy.</t>
+          <t>Tao biết. Chỉ nghĩ đến viễn cảnh đó thôi đã khiến tao rùng mình, chân run rẩy khi đối mặt với lũ quái vật ấy.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đúng vậy! Dù ta cố kéo thế nào, nó vẫn không nhúc nhích tí nào.</t>
+          <t>Đúng vậy! Dù tao cố kéo thế nào, nó vẫn không nhúc nhích tí nào.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Nghe giống ta thật.</t>
+          <t>Nghe giống tao thật.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>*Thở dài* Ta đang trở nên cả tin quá. Ngày trước ta còn cùng Carlow đi tìm Kiếm in the Rock mãi mà chẳng thấy gì...</t>
+          <t>*Thở dài* Ta đang trở nên cả tin quá. Ngày trước ta còn cùng Carlow đi tìm Kiếm đơn in the Rock mãi mà chẳng thấy gì...</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Ta muốn cảm ơn cậu!</t>
+          <t>Tao muốn cảm ơn cậu!</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Ta mà đầu bếp á? Ta mới làm phục vụ được có tí thôi.</t>
+          <t>Tao mà đầu bếp á? Tao mới làm phục vụ được có tí thôi.</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Ta muốn cảm ơn cậu!</t>
+          <t>Tao muốn cảm ơn cậu!</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ta mà đầu bếp á? Ta mới làm phục vụ được có tí thôi.</t>
+          <t>Tao mà đầu bếp á? Tao mới làm phục vụ được có tí thôi.</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Ta muốn cảm ơn cậu!</t>
+          <t>Tao muốn cảm ơn cậu!</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Ta mà đầu bếp á? Ta mới làm phục vụ được có tí thôi.</t>
+          <t>Tao mà đầu bếp á? Tao mới làm phục vụ được có tí thôi.</t>
         </is>
       </c>
     </row>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Ta à? Ta thì cái gì cũng được hết.</t>
+          <t>Tao à? Tao thì cái gì cũng được hết.</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tôi có thể chưa có nhiều kinh nghiệm, nhưng nếu cậu thuê tôi, tôi sẵn sàng lao vào và cống hiến hết mình!</t>
+          <t>Tôi có thể chưa có nhiều kinh nghiệm, nhưng nếu bạn thuê tôi, tôi sẵn sàng lao vào và cống hiến hết mình!</t>
         </is>
       </c>
     </row>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Cái này ta đãi. Ăn đi nào!</t>
+          <t>Cái này tao đãi. Ăn đi nào!</t>
         </is>
       </c>
     </row>
@@ -17090,7 +17090,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Nếu nấu được gì đó, cậu có thể nếm thử giúp ta không?</t>
+          <t>Nếu nấu được gì đó, cậu có thể nếm thử giúp tao không?</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Ta chưa bao giờ thấy ngươi hứng thú đến vậy.</t>
+          <t>Tao chưa bao giờ thấy mày hứng thú đến vậy.</t>
         </is>
       </c>
     </row>
@@ -20470,7 +20470,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Ta biết cậu chỉ đang tử tế thôi. Không sao đâu. Ta sẽ không để chuyện này ngăn mình thử lại lần nữa.</t>
+          <t>Tao biết cậu chỉ đang tử tế thôi. Không sao đâu. Tao sẽ không để chuyện này ngăn mình thử lại lần nữa.</t>
         </is>
       </c>
     </row>
@@ -20535,7 +20535,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Tất cả đều là lỗi của ta. Mấy nguyên liệu tốt này đều đổ sông đổ biển hết rồi.</t>
+          <t>Tất cả đều là lỗi của tao. Mấy nguyên liệu tốt này đều đổ sông đổ biển hết rồi.</t>
         </is>
       </c>
     </row>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Từ giờ trở đi, mục tiêu của ta là làm chủ nghệ thuật... không làm cháy đồ ăn!</t>
+          <t>Từ giờ trở đi, mục tiêu của tao là làm chủ nghệ thuật... không làm cháy đồ ăn!</t>
         </is>
       </c>
     </row>
@@ -21120,7 +21120,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Ủa?</t>
+          <t>Ờ?</t>
         </is>
       </c>
     </row>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Ta đã thử qua không biết bao nhiêu công thức, nhưng chưa bao giờ thực sự dốc lòng với cái nào cả. Có lẽ đã đến lúc quay về nơi bắt đầu.</t>
+          <t>Tao đã thử qua không biết bao nhiêu công thức, nhưng chưa bao giờ thực sự dốc lòng với cái nào cả. Có lẽ đã đến lúc quay về nơi bắt đầu.</t>
         </is>
       </c>
     </row>
@@ -22875,7 +22875,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Tất cả là nhờ sự hỗ trợ và chỉ dẫn của cậu! Nhưng mà... ta mới nhận ra mình còn chưa bao giờ hỏi cậu thích ăn gì...</t>
+          <t>Tất cả là nhờ sự hỗ trợ và chỉ dẫn của cậu! Nhưng mà... tao mới nhận ra mình còn chưa bao giờ hỏi cậu thích ăn gì...</t>
         </is>
       </c>
     </row>
@@ -23330,7 +23330,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -23720,7 +23720,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ta muốn cảm ơn cậu!</t>
+          <t>Tao muốn cảm ơn cậu!</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24435,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Ta mà đầu bếp á? Ta mới làm phục vụ được có tí thôi.</t>
+          <t>Tao mà đầu bếp á? Tao mới làm phục vụ được có tí thôi.</t>
         </is>
       </c>
     </row>
@@ -28075,7 +28075,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Ta từng nghe một câu nói: Tất cả âm nhạc trên thế gian này đều đã được thần linh viết sẵn, rải rác khắp nơi. Nhiệm vụ của người nhạc sĩ là tìm ra và ghi chép lại chúng.</t>
+          <t>Tao từng nghe một câu nói: Tất cả âm nhạc trên thế gian này đều đã được thần linh viết sẵn, rải rác khắp nơi. Nhiệm vụ của người nhạc sĩ là tìm ra và ghi chép lại chúng.</t>
         </is>
       </c>
     </row>
@@ -28595,7 +28595,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kỳ lạ thật. Họ cứ dẫn ta đi lòng vòng. Có vẻ không muốn ta đến gần dinh thự.</t>
+          <t>Kỳ lạ thật. Họ cứ dẫn tao đi lòng vòng. Có vẻ không muốn tao đến gần dinh thự.</t>
         </is>
       </c>
     </row>
@@ -29570,7 +29570,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nếu cậu bảo ông ấy nhận nuôi &lt;color=yellow&gt;orphan girl from the other side of the family&lt;/color&gt; ấy, thì thôi miễn bình luận. Tớ nghe rồi.</t>
+          <t>Nếu cậu bảo ông ấy nhận nuôi &lt;color=yellow&gt;đứa bé mồ côi bên họ hàng xa&lt;/color&gt; ấy, thì thôi miễn bình luận. Tớ nghe rồi.</t>
         </is>
       </c>
     </row>
@@ -29895,7 +29895,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>("Chỉ cần chạm nhẹ vào gương, ngay lập tức &lt;color=yellow&gt;memories, experiences&lt;/color&gt;, thậm chí cả những &lt;color=yellow&gt;thoughts&lt;/color&gt; của ta đều bị hút ra, tạo nên Sonoro này.")</t>
+          <t>("Chỉ cần chạm nhẹ vào gương, ngay lập tức &lt;color=yellow&gt;ký ức, trải nghiệm&lt;/color&gt;, thậm chí cả những &lt;color=yellow&gt;suy nghĩ thoáng qua&lt;/color&gt; của tao đều bị hút ra, tạo nên Sonoro này.")</t>
         </is>
       </c>
     </row>
@@ -30285,7 +30285,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Thực ra, ý hắn là tụi ta vừa thấy cậu đấy. Vừa nãy, ừm, khoảng một phút trước. Cậu đi ngang qua tụi ta và đi về hướng kia ấy.</t>
+          <t>Thực ra, ý hắn là tụi tao vừa thấy cậu đấy. Vừa nãy, ừm, khoảng một phút trước. Cậu đi ngang qua tụi tao và đi về hướng kia ấy.</t>
         </is>
       </c>
     </row>
@@ -30415,7 +30415,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Bộ đồ của cậu... Không, chính là phụ kiện ấy. Của cậu màu đỏ, nhưng người ta tôi thấy đeo cái màu &lt;color=yellow&gt;blue&lt;/color&gt; trên cổ tay... Hmm. Có lẽ tôi chỉ tưởng tượng thôi.</t>
+          <t>Bộ đồ của cậu... Không, chính là phụ kiện ấy. Của cậu màu đỏ, nhưng người ta tôi thấy đeo cái màu &lt;color=yellow&gt;xanh dương&lt;/color&gt; trên cổ tay... Hmm. Có lẽ tôi chỉ tưởng tượng thôi.</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Ừ, giờ ta nhớ rồi... buổi tập hợp bị trễ giờ vì &lt;color=yellow&gt;lighting&lt;/color&gt; bị trục trặc...</t>
+          <t>Ừ, giờ tao nhớ rồi... buổi tập hợp bị trễ giờ vì &lt;color=yellow&gt;hệ thống chiếu sáng&lt;/color&gt; bị trục trặc...</t>
         </is>
       </c>
     </row>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tôi đang xem lại những gì đã xảy ra &lt;color=yellow&gt;eleven years ago&lt;/color&gt;...</t>
+          <t>Tôi đang xem lại những gì đã xảy ra &lt;color=yellow&gt;mười một năm trước&lt;/color&gt;...</t>
         </is>
       </c>
     </row>
@@ -31585,7 +31585,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Cảm giác như ta đang sống lại &lt;color=yellow&gt;the past&lt;/color&gt; vậy...</t>
+          <t>Cảm giác như ta đang sống lại &lt;color=yellow&gt;quá khứ&lt;/color&gt; vậy...</t>
         </is>
       </c>
     </row>
@@ -31650,7 +31650,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Đây &lt;color=yellow&gt;not exactly how it happened&lt;/color&gt;.</t>
+          <t>Đây &lt;color=yellow&gt;không phải những gì đã xảy ra thật sự&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32432,7 +32432,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Không, những đồ trang trí này... không phải thật đâu, dù nhìn y như thật. Đây chỉ là một mô phỏng khác từ &lt;color=yellow&gt;my memories&lt;/color&gt;.</t>
+          <t>Không, những đồ trang trí này... không phải thật đâu, dù nhìn y như thật. Đây chỉ là một mô phỏng khác từ &lt;color=yellow&gt;ký ức của ta&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32497,7 +32497,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Giờ thì, câu hỏi là… &lt;color=yellow&gt;What moment from my past&lt;/color&gt; mà điều này đại diện?</t>
+          <t>Giờ thì, câu hỏi là… &lt;color=yellow&gt;Khoảnh khắc nào trong quá khứ của ta&lt;/color&gt; mà điều này đại diện?</t>
         </is>
       </c>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Đừng có so sánh chúng ta với nhau. Và đừng nhắc đến cái tên Montelli bằng cái miệng dơ bẩn của ngươi.</t>
+          <t>Đừng có so sánh chúng ta với nhau. Và đừng nhắc đến cái tên Montelli bằng cái miệng dơ bẩn của mày.</t>
         </is>
       </c>
     </row>
